--- a/samples/corpus/full/chantiers/ecole-montferrine/1-marche/dpgf/DEV-2026-031_indice-B_dpgf-ecole-du-bourg.xlsx
+++ b/samples/corpus/full/chantiers/ecole-montferrine/1-marche/dpgf/DEV-2026-031_indice-B_dpgf-ecole-du-bourg.xlsx
@@ -776,7 +776,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Modifications après la réunion de négociation du 06/03/2026 : ajout des deux fenêtres de la bibliothèque à la demande de la commune (postes 2 et 3 : 16 fenêtres au lieu de 14) ; prix unitaire de l'isolation des plafonds (poste 4) ramené de 54,00 € à 51,50 € HT ; poste 6 ramené de 16400,00 € à 15900,00 € HT.</t>
+          <t>Modification de consistance demandée par la commune lors de la réunion de négociation du 06/03/2026 : ajout des deux fenêtres de la bibliothèque à la demande de la commune (postes 2 et 3 : 16 fenêtres au lieu de 14) ; prix unitaire de l'isolation des plafonds (poste 4) ramené de 54,00 € à 51,50 € HT ; poste 6 ramené de 16400,00 € à 15900,00 € HT.</t>
         </is>
       </c>
     </row>
